--- a/backend/app/data/seed.xlsx
+++ b/backend/app/data/seed.xlsx
@@ -1737,7 +1737,7 @@
         <v>83</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>35</v>
+        <v>-35</v>
       </c>
       <c r="D5" s="16" t="n">
         <v>0.9</v>
